--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008510362272481009</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>37410270</v>
+        <v>4160167</v>
       </c>
       <c r="L2" t="n">
-        <v>14031173</v>
+        <v>1546404</v>
       </c>
       <c r="M2" t="n">
-        <v>2598678</v>
+        <v>288228</v>
       </c>
       <c r="N2" t="n">
-        <v>57513</v>
+        <v>6508</v>
       </c>
       <c r="O2" t="n">
-        <v>1554660</v>
+        <v>170482</v>
       </c>
       <c r="P2" t="n">
-        <v>28594</v>
+        <v>2983</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999243021011353</v>
+        <v>0.9999485015869141</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7144233584403992</v>
+        <v>0.7073312997817993</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5361683964729309</v>
+        <v>0.5400761961936951</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4034346044063568</v>
+        <v>0.4079007804393768</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04547654092311859</v>
+        <v>0.04644722864031792</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4046143889427185</v>
+        <v>0.4076195955276489</v>
       </c>
       <c r="W2" t="n">
-        <v>0.451814740896225</v>
+        <v>0.4570946991443634</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002038439189791413</v>
       </c>
       <c r="C3" t="n">
-        <v>542</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
-        <v>37410270</v>
+        <v>4160167</v>
       </c>
       <c r="E3" t="n">
-        <v>7326880</v>
+        <v>776509</v>
       </c>
       <c r="F3" t="n">
-        <v>314782</v>
+        <v>32482</v>
       </c>
       <c r="G3" t="n">
-        <v>34861</v>
+        <v>3674</v>
       </c>
       <c r="H3" t="n">
-        <v>27068</v>
+        <v>2640</v>
       </c>
       <c r="I3" t="n">
-        <v>1225</v>
+        <v>121</v>
       </c>
       <c r="J3" t="n">
-        <v>90145298</v>
+        <v>10016297</v>
       </c>
       <c r="K3" t="n">
-        <v>86896755</v>
+        <v>9632615</v>
       </c>
       <c r="L3" t="n">
-        <v>105338046</v>
+        <v>11706373</v>
       </c>
       <c r="M3" t="n">
-        <v>134712995</v>
+        <v>14971336</v>
       </c>
       <c r="N3" t="n">
-        <v>144955483</v>
+        <v>16106295</v>
       </c>
       <c r="O3" t="n">
-        <v>140090214</v>
+        <v>15570463</v>
       </c>
       <c r="P3" t="n">
-        <v>145190899</v>
+        <v>16132371</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8292086720466614</v>
+        <v>0.8361043930053711</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4757912456989288</v>
+        <v>0.4677109718322754</v>
       </c>
       <c r="T3" t="n">
-        <v>0.308972954750061</v>
+        <v>0.3066650032997131</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07155530154705048</v>
+        <v>0.07255537807941437</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3388150632381439</v>
+        <v>0.3333756923675537</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01642570644617081</v>
+        <v>0.01540121622383595</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03213413144859563</v>
       </c>
       <c r="C4" t="n">
-        <v>254</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>13276254</v>
+        <v>1526303</v>
       </c>
       <c r="E4" t="n">
-        <v>14031173</v>
+        <v>1546404</v>
       </c>
       <c r="F4" t="n">
-        <v>1701025</v>
+        <v>182202</v>
       </c>
       <c r="G4" t="n">
-        <v>192492</v>
+        <v>20864</v>
       </c>
       <c r="H4" t="n">
-        <v>284200</v>
+        <v>30035</v>
       </c>
       <c r="I4" t="n">
-        <v>4790</v>
+        <v>477</v>
       </c>
       <c r="J4" t="n">
-        <v>4300</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>14954017</v>
+        <v>1721330</v>
       </c>
       <c r="L4" t="n">
-        <v>12138166</v>
+        <v>1316903</v>
       </c>
       <c r="M4" t="n">
-        <v>3842708</v>
+        <v>418385</v>
       </c>
       <c r="N4" t="n">
-        <v>1207161</v>
+        <v>133608</v>
       </c>
       <c r="O4" t="n">
-        <v>2287665</v>
+        <v>247756</v>
       </c>
       <c r="P4" t="n">
-        <v>34693</v>
+        <v>3543</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999621510505676</v>
+        <v>0.999974250793457</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7675482630729675</v>
+        <v>0.7663459181785583</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5041787028312683</v>
+        <v>0.5012954473495483</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3499411940574646</v>
+        <v>0.3501116633415222</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0556102953851223</v>
+        <v>0.05663735046982765</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3688028454780579</v>
+        <v>0.3667782247066498</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03169899806380272</v>
+        <v>0.02979841269552708</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>576</v>
+        <v>54</v>
       </c>
       <c r="D5" t="n">
-        <v>1241651</v>
+        <v>144454</v>
       </c>
       <c r="E5" t="n">
-        <v>3555652</v>
+        <v>397194</v>
       </c>
       <c r="F5" t="n">
-        <v>2598678</v>
+        <v>288228</v>
       </c>
       <c r="G5" t="n">
-        <v>313339</v>
+        <v>34766</v>
       </c>
       <c r="H5" t="n">
-        <v>692330</v>
+        <v>74300</v>
       </c>
       <c r="I5" t="n">
-        <v>8471</v>
+        <v>883</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7705358</v>
+        <v>815488</v>
       </c>
       <c r="L5" t="n">
-        <v>15459015</v>
+        <v>1759920</v>
       </c>
       <c r="M5" t="n">
-        <v>5812019</v>
+        <v>651651</v>
       </c>
       <c r="N5" t="n">
-        <v>746243</v>
+        <v>83189</v>
       </c>
       <c r="O5" t="n">
-        <v>3033861</v>
+        <v>340899</v>
       </c>
       <c r="P5" t="n">
-        <v>1712214</v>
+        <v>190703</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999707341194153</v>
+        <v>0.999980092048645</v>
       </c>
       <c r="R5" t="n">
-        <v>0.845819354057312</v>
+        <v>0.844649076461792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8122211694717407</v>
+        <v>0.8115800023078918</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9343065619468689</v>
+        <v>0.9344726204872131</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9867085218429565</v>
+        <v>0.9867236614227295</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9637908935546875</v>
+        <v>0.9639516472816467</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9881135821342468</v>
+        <v>0.9881046414375305</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>341</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>222110</v>
+        <v>25857</v>
       </c>
       <c r="E6" t="n">
-        <v>234043</v>
+        <v>25953</v>
       </c>
       <c r="F6" t="n">
-        <v>214985</v>
+        <v>23422</v>
       </c>
       <c r="G6" t="n">
-        <v>57513</v>
+        <v>6508</v>
       </c>
       <c r="H6" t="n">
-        <v>72810</v>
+        <v>7761</v>
       </c>
       <c r="I6" t="n">
-        <v>1954</v>
+        <v>174</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1164</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
-        <v>195278</v>
+        <v>22443</v>
       </c>
       <c r="E7" t="n">
-        <v>907235</v>
+        <v>103832</v>
       </c>
       <c r="F7" t="n">
-        <v>1376420</v>
+        <v>153682</v>
       </c>
       <c r="G7" t="n">
-        <v>535511</v>
+        <v>58996</v>
       </c>
       <c r="H7" t="n">
-        <v>1554660</v>
+        <v>170482</v>
       </c>
       <c r="I7" t="n">
-        <v>18253</v>
+        <v>1888</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1423</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>18724</v>
+        <v>2273</v>
       </c>
       <c r="E8" t="n">
-        <v>114356</v>
+        <v>13415</v>
       </c>
       <c r="F8" t="n">
-        <v>235496</v>
+        <v>26597</v>
       </c>
       <c r="G8" t="n">
-        <v>130958</v>
+        <v>15308</v>
       </c>
       <c r="H8" t="n">
-        <v>1211257</v>
+        <v>133020</v>
       </c>
       <c r="I8" t="n">
-        <v>28594</v>
+        <v>2983</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
